--- a/announcements.xlsx
+++ b/announcements.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="公告" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="字段说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="奖励" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="字段说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,169 +431,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>版本名</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>版本号</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>详情中文</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tag</t>
+          <t>详情英文</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>详情日文</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>important</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>min_code</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>max_code</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>lang</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
+          <t>详情韩文</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="110" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A20260909001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>新版本 0.1.6.4 更新内容</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>V 0.1.6.3</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>185</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>版本号:V 0.1.6.3
+1.增强技能伤害范围；
+2.资源获得更容易；
+3.提升广告响应速度：
+4.修复若干Bug。</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Version:V 0.1.6.3
+1.Enhance skill damage range;
+2.Make resources easier to obtain;
+3.Improve ad response speed;
+4.Fix several bugs.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1. 优化了低端机型的帧率表现
-2. 新增战斗中随机奖励热气球
-3. 修复若干已知问题</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>185</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A20260909002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>周末双倍活动开启</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>活动</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>本周六、周日全天金币掉落翻倍，别忘了上线。</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
+          <t>バージョン:V 0.1.6.3
+1.スキルのダメージ範囲を強化；
+2.リソースの獲得を容易に；
+3.広告の応答速度を向上；
+4.いくつかのバグを修正。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>버전:V 0.1.6.3
+1.스킬 피해 범위 강화；
+2.자원 획득 용이；
+3.광고 응답 속도 향상；
+4.여러 버그 수정。</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -606,26 +531,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>奖励名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>奖励数量</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>金币</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>更新奖励</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>钻石</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>600</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>更新奖励</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
+          <t>工作表</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -634,187 +647,220 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>公告</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>版本名</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>字符串</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>公告唯一 ID，用于记录已读。不要重复，也不要修改已发布过的 ID</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>显示用的版本号文字，例如 V 0.1.6.3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>公告</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>字符串</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>标题</t>
+          <t>版本号</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>数字</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>versionCode，用来判断是不是新版本（185 = 0.1.6.3）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>公告</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>详情中文</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>字符串</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>日期，写成 2026-09-09 这种格式</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>对应 ST_公告结构体.详情中文，单元格内 Alt+Enter 换行</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tag</t>
+          <t>公告</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>详情英文</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>字符串</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>标签：更新 / 活动 / 维护 / 补偿 / 公告</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>对应 ST_公告结构体.详情英文</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>公告</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>详情日文</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>字符串</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>正文。单元格内用 Alt+Enter 换行</t>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>对应 ST_公告结构体.详情日文</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>公告</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>详情韩文</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>字符串</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>配图地址，可留空</t>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>对应 ST_公告结构体.详情韩文</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>important</t>
+          <t>奖励</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TRUE/FALSE</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>TRUE = 进游戏强制弹窗；FALSE = 只在公告列表里显示</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>字符串</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>对应奖励结构体的 ID，金币=3，钻石=4，不要用错</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>min_code</t>
+          <t>奖励</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>数字</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>最低版本号(versionCode)才显示，0 表示不限</t>
+          <t>奖励名称</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>字符串</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>金币 / 钻石</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>max_code</t>
+          <t>奖励</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>奖励数量</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>数字</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>最高版本号，0 表示不限</t>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>这次更新发放的数量，改这里即可，不用改游戏</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lang</t>
+          <t>奖励</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>字符串</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>zh 中文 / en 英文</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TRUE/FALSE</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>FALSE = 这条不下发，等于临时下线</t>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>给自己看的说明，不会进 JSON</t>
         </is>
       </c>
     </row>
